--- a/autopiezas.beta.xlsx
+++ b/autopiezas.beta.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="37">
   <si>
     <t>cod_grupo</t>
   </si>
@@ -92,6 +92,36 @@
   </si>
   <si>
     <t>14,5</t>
+  </si>
+  <si>
+    <t>10,2</t>
+  </si>
+  <si>
+    <t>9,8</t>
+  </si>
+  <si>
+    <t>12,9</t>
+  </si>
+  <si>
+    <t>8,7</t>
+  </si>
+  <si>
+    <t>14,3</t>
+  </si>
+  <si>
+    <t>55,95</t>
+  </si>
+  <si>
+    <t>69,1</t>
+  </si>
+  <si>
+    <t>M1-19133</t>
+  </si>
+  <si>
+    <t>M1-19134</t>
+  </si>
+  <si>
+    <t>M1-19136</t>
   </si>
 </sst>
 </file>
@@ -575,6 +605,342 @@
         <v>0.0</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="5">
+        <v>33.0</v>
+      </c>
+      <c r="N5" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="O5" s="4">
+        <v>11759.0</v>
+      </c>
+      <c r="P5" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="Q5" s="6">
+        <v>11.0</v>
+      </c>
+      <c r="R5" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="S5" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="T5" s="6">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="5">
+        <v>7.0</v>
+      </c>
+      <c r="N6" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="O6" s="4">
+        <v>11760.0</v>
+      </c>
+      <c r="P6" s="6">
+        <v>7.0</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>11.0</v>
+      </c>
+      <c r="R6" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="S6" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="T6" s="6">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="5">
+        <v>48.0</v>
+      </c>
+      <c r="N7" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="O7" s="4">
+        <v>11762.0</v>
+      </c>
+      <c r="P7" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="Q7" s="6">
+        <v>16.0</v>
+      </c>
+      <c r="R7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S7" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="T7" s="6">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="5">
+        <v>14.0</v>
+      </c>
+      <c r="N8" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="O8" s="4">
+        <v>11763.0</v>
+      </c>
+      <c r="P8" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q8" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="R8" s="6">
+        <v>10.0</v>
+      </c>
+      <c r="S8" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="T8" s="6">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="5">
+        <v>368.0</v>
+      </c>
+      <c r="N9" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="O9" s="4">
+        <v>90137.0</v>
+      </c>
+      <c r="P9" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q9" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="R9" s="6">
+        <v>10.0</v>
+      </c>
+      <c r="S9" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="T9" s="6">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="N10" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="O10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="P10" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="Q10" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="R10" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="S10" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="T10" s="6">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="N11" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="O11" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="P11" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="Q11" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="R11" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="S11" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="T11" s="6">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="N12" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="O12" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="P12" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="Q12" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="R12" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="S12" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="T12" s="6">
+        <v>0.0</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
